--- a/FOA Singles/Uncategorized-Single.xlsx
+++ b/FOA Singles/Uncategorized-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -585,7 +585,6 @@
           <t>M-CareKit-A</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit</t>
@@ -595,7 +594,7 @@
         <is>
           <t>FREE SHIPPING
 CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit is designed to complement your space with a balanced, versatile look.
-Product Dimensions: 8.25" W x 2" x 7.5" H
+Product Dimensions: 8.25" W X 2" X 7.5" H
 Weight: 2.25 lbs</t>
         </is>
       </c>

--- a/FOA Singles/Uncategorized-Single.xlsx
+++ b/FOA Singles/Uncategorized-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,168 +429,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Subcategory</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>seo title(70char)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>seo title(70char)</t>
+          <t>seo description(160char)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>seo description(160char)</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Short Description</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Short Description</t>
+          <t>Short Description - Red Text</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Short Description - Red Text</t>
+          <t>Item Type</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Parts for Group Items</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Parts for Group Items</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>East(cost)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>East(cost)</t>
+          <t>EAST COST (Updated)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>EAST COST (Updated)</t>
+          <t>MSRP</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>MSRP</t>
+          <t>Weight (LB)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Weight (LB)</t>
+          <t>Product Dimension (Inch)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Product Dimension (Inch)</t>
+          <t>Style</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Style</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Shipping Length (IN)</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Shipping Length (IN)</t>
+          <t>Shipping Width (IN)</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Shipping Width (IN)</t>
+          <t>Shipping Height (IN)</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Shipping Height (IN)</t>
+          <t>Volume (CUFT)</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Volume (CUFT)</t>
+          <t>Fixed tags</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Variable tags</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>M-CareKit-A</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit is designed to complement your space with a balanced, versatile look.
@@ -598,74 +603,84 @@
 Weight: 2.25 lbs</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care | GOODDEGG</t>
+          <t>CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit brings everyday comfort. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit brings everyday comfort. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CLEAN LIVING FURNITURE CARE KIT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Clean Living Furniture Care Kit</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Single Item</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>M-CareKit-A-1.jpg,M-CAREKIT-A-2.jpg,M-CAREKIT-A-3.jpg,M-CAREKIT-A-4.jpg</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="R2" t="n">
+        <v>45</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>8.25" W X 2" X 7.5" H</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>FURNITURE POLISH. Improves appearance of finished wood surfaces by removing dust and fingerprints.,UPHOLSTERY CLEANER. Cleans tough stains on fabric, leather, and vinyl to help prolong the life of your furniture.,LEATHER CONDITIONER. Aids in revitalizing your leather and vinyl furniture to its restored condition.,FURNITURE PROTECTOR. Helps repel liquids, dirt, and stain from all types of furniture materials.</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
           <t>CLEAN LIVING FURNITURE CARE KIT</t>
         </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Clean Living Furniture Care Kit</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Single Item</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>M-CareKit-A-1.jpg,M-CAREKIT-A-2.jpg,M-CAREKIT-A-3.jpg,M-CAREKIT-A-4.jpg</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>15</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S2" t="n">
-        <v>45</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>8.25" W X 2" X 7.5" H</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>FURNITURE POLISH. Improves appearance of finished wood surfaces by removing dust and fingerprints.,UPHOLSTERY CLEANER. Cleans tough stains on fabric, leather, and vinyl to help prolong the life of your furniture.,LEATHER CONDITIONER. Aids in revitalizing your leather and vinyl furniture to its restored condition.,FURNITURE PROTECTOR. Helps repel liquids, dirt, and stain from all types of furniture materials.</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="Z2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/FOA Singles/Uncategorized-Single.xlsx
+++ b/FOA Singles/Uncategorized-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -597,10 +597,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit is designed to complement your space with a balanced, versatile look.
-Product Dimensions: 8.25" W X 2" X 7.5" H
-Weight: 2.25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit is designed to complement your space with a balanced, versatile look.&lt;br&gt;
+Product Dimensions: 8.25" W X 2" X 7.5" H&lt;br&gt;
+Weight: 2.25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/FOA Singles/Uncategorized-Single.xlsx
+++ b/FOA Singles/Uncategorized-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,6 +583,21 @@
           <t>Variable tags</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="C2" t="inlineStr">
@@ -680,6 +695,16 @@
       <c r="AD2" t="inlineStr">
         <is>
           <t>CLEAN LIVING FURNITURE CARE KIT</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
         </is>
       </c>
     </row>

--- a/FOA Singles/Uncategorized-Single.xlsx
+++ b/FOA Singles/Uncategorized-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">

--- a/FOA Singles/Uncategorized-Single.xlsx
+++ b/FOA Singles/Uncategorized-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -620,12 +620,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care | GOODDEGG</t>
+          <t>LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit brings everyday comfort. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LIVING FURNITURE CARE KIT Clean Living supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/FOA Singles/Uncategorized-Single.xlsx
+++ b/FOA Singles/Uncategorized-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/FOA Singles/Uncategorized-Single.xlsx
+++ b/FOA Singles/Uncategorized-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/FOA Singles/Uncategorized-Single.xlsx
+++ b/FOA Singles/Uncategorized-Single.xlsx
@@ -429,188 +429,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>seo title(70char)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>seo description(160char)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Short Description</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Short Description - Red Text</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Item Type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Parts for Group Items</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Images</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Image src</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>combine image src</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>East(cost)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>EAST COST (Updated)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MSRP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Weight (LB)</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Product Dimension (Inch)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Shipping Length (IN)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Shipping Width (IN)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Shipping Height (IN)</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Volume (CUFT)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Fixed tags</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Variable tags</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean-living-furniture-care-kit-clean-living-furniture-care-kit</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>M-CareKit-A</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 CLEAN LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit is designed to complement your space with a balanced, versatile look.&lt;br&gt;
@@ -618,91 +638,97 @@
 Weight: 2.25 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>LIVING FURNITURE CARE KIT Clean Living Furniture Care Kit | GOODDEGG</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>LIVING FURNITURE CARE KIT Clean Living supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>CLEAN LIVING FURNITURE CARE KIT</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Clean Living Furniture Care Kit</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>M-CareKit-A-1.jpg,M-CAREKIT-A-2.jpg,M-CAREKIT-A-3.jpg,M-CAREKIT-A-4.jpg</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>M-CareKit-A-1.jpg,M-CAREKIT-A-2.jpg,M-CAREKIT-A-3.jpg,M-CAREKIT-A-4.jpg</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>15</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="T2" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>45</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>2.25</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>8.25" W X 2" X 7.5" H</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>FURNITURE POLISH. Improves appearance of finished wood surfaces by removing dust and fingerprints.,UPHOLSTERY CLEANER. Cleans tough stains on fabric, leather, and vinyl to help prolong the life of your furniture.,LEATHER CONDITIONER. Aids in revitalizing your leather and vinyl furniture to its restored condition.,FURNITURE PROTECTOR. Helps repel liquids, dirt, and stain from all types of furniture materials.</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
         <v>7.5</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>0.1</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>CLEAN LIVING FURNITURE CARE KIT</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
